--- a/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
+++ b/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,51 +443,31 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Basicas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Escalon debajo de nro 1</t>
+          <t>Prioridad estetica</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad baja</t>
+          <t>Las numero 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Los no modernos</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Baratos pero calidad acorde</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>169</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
+++ b/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
@@ -443,31 +443,31 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Basicas</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Prioridad estetica</t>
+          <t>Escalon debajo de numero 1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Las numero 1</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
+++ b/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
@@ -443,17 +443,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Mejor calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Escalon debajo de numero 1</t>
+          <t>Calidad media</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -463,11 +463,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Baja calidad</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
+++ b/data/modelling/clustering/smartband/df_alt_per_clust.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,31 +443,31 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mejor calidad</t>
+          <t>Alta calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Calidad media</t>
+          <t>Baja calidad</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baja calidad</t>
+          <t>Media calidad</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
